--- a/quizzes/peinture-18e-niveau1.xlsx
+++ b/quizzes/peinture-18e-niveau1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFEDD3A9-74D8-4B7B-8400-22A2C0812496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9052BD32-2845-4913-BAC3-7AC42D59E108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D010EE7-3957-4632-B43B-1193B29575F7}"/>
   </bookViews>
@@ -77,9 +77,6 @@
     <t>François Boucher</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1742</t>
   </si>
   <si>
@@ -119,9 +116,6 @@
     <t>La Raie</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/3/35/Jacques-Louis_David%2C_Le_Serment_des_Horaces.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Jacques-Louis David</t>
   </si>
   <si>
@@ -131,9 +125,6 @@
     <t>Le Serment des Horaces</t>
   </si>
   <si>
-    <t>Élisabeth Vigée Le Brun</t>
-  </si>
-  <si>
     <t>1787</t>
   </si>
   <si>
@@ -227,9 +218,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Jean-Baptiste_Greuze_-_The_Village_Agreement.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/ec/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UK.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/52/Thomas_Gainsborough_-_Mr_and_Mrs_Andrews.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -248,9 +236,6 @@
     <t>1785</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Johann Zoffany</t>
   </si>
   <si>
@@ -284,9 +269,6 @@
     <t>Museo del Prado, Madrid</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Canaletto</t>
   </si>
   <si>
@@ -308,9 +290,6 @@
     <t>Musée des Beaux-Arts, Houston</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/10/Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Pietro Longhi</t>
   </si>
   <si>
@@ -341,9 +320,6 @@
     <t>Pompeo Batoni</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/Pompeo_Batoni_-_Emperor_Joseph_II_with_Grand_Duke_Pietro_Leopoldo_of_Tuscany_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>1769</t>
   </si>
   <si>
@@ -362,9 +338,6 @@
     <t>Vue de Dresde depuis la rive droite de l'Elbe</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/El_Quitasol_%28Goya%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Francisco de Goya</t>
   </si>
   <si>
@@ -392,9 +365,6 @@
     <t>Le Parnasse</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/56/John_Henry_Fuseli_-_The_Nightmare.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Henry Fuseli</t>
   </si>
   <si>
@@ -422,9 +392,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Charles-Andr%C3%A9%2C_dit_Carle_Vanloo_-_Halte_de_chasse_%281737%29.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Carle Van Loo</t>
-  </si>
-  <si>
     <t>1737</t>
   </si>
   <si>
@@ -452,13 +419,46 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/8/8a/Ad%C3%A9la%C3%AFde_Labille-Guiard_-_Self-Portrait_with_Two_Pupils_-_The_Metropolitan_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Adélaïde Labille-Guiard</t>
-  </si>
-  <si>
     <t>Autoportrait avec deux élèves</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/El_Quitasol_%28Goya%29.jpg/1280px-El_Quitasol_%28Goya%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/33/Pompeo_Batoni_002.jpg/960px-Pompeo_Batoni_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/John_Henry_Fuseli_-_The_Nightmare.JPG/1280px-John_Henry_Fuseli_-_The_Nightmare.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg/960px-Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Adélaïde LABILLE-GUIARD</t>
+  </si>
+  <si>
+    <t>Carle van LOO</t>
+  </si>
+  <si>
+    <t>Élisabeth VIGEE LE BRUN</t>
   </si>
 </sst>
 </file>
@@ -492,7 +492,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -503,6 +503,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC54F38"/>
         <bgColor rgb="FFC54F38"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -556,7 +562,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -572,6 +578,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -936,539 +944,544 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>137</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>25</v>
+      <c r="A5" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="E8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="5" t="s">
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1783</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>51</v>
+      <c r="E11" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="B16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>81</v>
+      <c r="A17" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>83</v>
+        <v>120</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1721</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" s="6">
-        <v>1783</v>
+        <v>123</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="4" t="s">
-        <v>100</v>
+      <c r="A21" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>103</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>106</v>
+      <c r="A22" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="4" t="s">
-        <v>113</v>
+      <c r="A25" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>125</v>
+      <c r="A27" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>129</v>
+      <c r="A28" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" s="6">
-        <v>1721</v>
+        <v>87</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="4" t="s">
-        <v>133</v>
+      <c r="A30" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="4" t="s">
-        <v>136</v>
+      <c r="A31" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
+    <sortCondition ref="B2:B31"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{9FE834A6-ECEF-4986-A577-79A3855787E1}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{1177A6F2-E6B2-476E-A2A6-B0E82CDAA77D}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{050A610E-B724-4EF6-A305-61DFFF57E08C}"/>
-    <hyperlink ref="A13" r:id="rId6" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
-    <hyperlink ref="A11" r:id="rId8" xr:uid="{68A68607-7EA8-4768-B5B9-A112A4C6A9EF}"/>
-    <hyperlink ref="A18" r:id="rId9" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
-    <hyperlink ref="A31" r:id="rId10" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
-    <hyperlink ref="A30" r:id="rId11" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
-    <hyperlink ref="A27" r:id="rId12" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
-    <hyperlink ref="A28" r:id="rId13" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
-    <hyperlink ref="A29" r:id="rId14" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
-    <hyperlink ref="A23" r:id="rId15" xr:uid="{4FFEF3FA-A758-444F-A755-C3C1C569C014}"/>
-    <hyperlink ref="A24" r:id="rId16" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
-    <hyperlink ref="A25" r:id="rId17" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
-    <hyperlink ref="A26" r:id="rId18" xr:uid="{9608CD97-2B71-4393-BBDE-35018F637ED3}"/>
-    <hyperlink ref="A22" r:id="rId19" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
-    <hyperlink ref="A19" r:id="rId20" xr:uid="{4AF5ADFF-1ADB-4C17-969C-DB8FB9AA6271}"/>
-    <hyperlink ref="A20" r:id="rId21" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
-    <hyperlink ref="A21" r:id="rId22" xr:uid="{D41BE3A6-CFDA-4DD2-BE2D-40A241CB5ECA}"/>
-    <hyperlink ref="A7" r:id="rId23" xr:uid="{9E3FA052-CC3D-4324-80BE-C2D78C611A6F}"/>
+    <hyperlink ref="A15" r:id="rId1" xr:uid="{9FE834A6-ECEF-4986-A577-79A3855787E1}"/>
+    <hyperlink ref="A20" r:id="rId2" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
+    <hyperlink ref="A19" r:id="rId3" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
+    <hyperlink ref="A23" r:id="rId4" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
+    <hyperlink ref="A16" r:id="rId5" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
+    <hyperlink ref="A9" r:id="rId6" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
+    <hyperlink ref="A2" r:id="rId7" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
+    <hyperlink ref="A18" r:id="rId8" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
+    <hyperlink ref="A26" r:id="rId9" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
+    <hyperlink ref="A6" r:id="rId10" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
+    <hyperlink ref="A17" r:id="rId11" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
+    <hyperlink ref="A24" r:id="rId12" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
+    <hyperlink ref="A3" r:id="rId13" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
+    <hyperlink ref="A4" r:id="rId14" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
+    <hyperlink ref="A29" r:id="rId15" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
+    <hyperlink ref="A5" r:id="rId16" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7668830C-59B8-4F92-879B-70324BB4D193}"/>
+    <hyperlink ref="A10" r:id="rId17" xr:uid="{4BA6EDCC-0531-4670-8770-157ADAE79A8E}"/>
+    <hyperlink ref="A7" r:id="rId18" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9D43AAAD-369E-43AE-836A-CE6A07DD65E2}"/>
+    <hyperlink ref="A14" r:id="rId19" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{54C5D1D3-C6E7-42ED-8E11-7CCA9C54BE78}"/>
+    <hyperlink ref="A28" r:id="rId20" xr:uid="{EBBB6BDC-96BE-4B7D-BE1C-1C8857858E2A}"/>
+    <hyperlink ref="A8" r:id="rId21" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{208417A7-5641-41CD-8C4F-D1A4EA68649D}"/>
+    <hyperlink ref="A13" r:id="rId22" xr:uid="{A0E64583-F066-467D-8CFA-63569F8AB875}"/>
+    <hyperlink ref="A27" r:id="rId23" xr:uid="{8FAE38C7-9C93-4CA9-9FF2-70DF5F01DDC1}"/>
+    <hyperlink ref="A22" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C1EC1DA-CA57-42F4-A3AA-A0A0588F399B}"/>
+    <hyperlink ref="A11" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9785A814-9B30-4822-BC9E-D804419A01D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-18e-niveau1.xlsx
+++ b/quizzes/peinture-18e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9052BD32-2845-4913-BAC3-7AC42D59E108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EE9E43-E8F5-4228-AA03-AC11414BDE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D010EE7-3957-4632-B43B-1193B29575F7}"/>
   </bookViews>
@@ -56,9 +56,6 @@
     <t>titre de l’œuvre</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Jean-Antoine Watteau</t>
   </si>
   <si>
@@ -459,6 +456,9 @@
   </si>
   <si>
     <t>Élisabeth VIGEE LE BRUN</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg/1280px-L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -944,512 +944,512 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>47</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" s="6">
         <v>1783</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="8" t="s">
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>8</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="C17" s="6">
         <v>1721</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1">
       <c r="A18" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="E22" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="8" t="s">
+      <c r="E27" s="8" t="s">
         <v>84</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="D28" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="E28" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1457,31 +1457,31 @@
     <sortCondition ref="B2:B31"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A15" r:id="rId1" xr:uid="{9FE834A6-ECEF-4986-A577-79A3855787E1}"/>
-    <hyperlink ref="A20" r:id="rId2" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
-    <hyperlink ref="A19" r:id="rId3" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
-    <hyperlink ref="A23" r:id="rId4" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
-    <hyperlink ref="A16" r:id="rId5" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
-    <hyperlink ref="A9" r:id="rId6" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
-    <hyperlink ref="A2" r:id="rId7" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
-    <hyperlink ref="A18" r:id="rId8" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
-    <hyperlink ref="A26" r:id="rId9" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
-    <hyperlink ref="A6" r:id="rId10" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
-    <hyperlink ref="A17" r:id="rId11" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
-    <hyperlink ref="A24" r:id="rId12" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
-    <hyperlink ref="A3" r:id="rId13" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
-    <hyperlink ref="A4" r:id="rId14" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
-    <hyperlink ref="A29" r:id="rId15" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
-    <hyperlink ref="A5" r:id="rId16" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7668830C-59B8-4F92-879B-70324BB4D193}"/>
-    <hyperlink ref="A10" r:id="rId17" xr:uid="{4BA6EDCC-0531-4670-8770-157ADAE79A8E}"/>
-    <hyperlink ref="A7" r:id="rId18" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9D43AAAD-369E-43AE-836A-CE6A07DD65E2}"/>
-    <hyperlink ref="A14" r:id="rId19" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{54C5D1D3-C6E7-42ED-8E11-7CCA9C54BE78}"/>
-    <hyperlink ref="A28" r:id="rId20" xr:uid="{EBBB6BDC-96BE-4B7D-BE1C-1C8857858E2A}"/>
-    <hyperlink ref="A8" r:id="rId21" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{208417A7-5641-41CD-8C4F-D1A4EA68649D}"/>
-    <hyperlink ref="A13" r:id="rId22" xr:uid="{A0E64583-F066-467D-8CFA-63569F8AB875}"/>
-    <hyperlink ref="A27" r:id="rId23" xr:uid="{8FAE38C7-9C93-4CA9-9FF2-70DF5F01DDC1}"/>
-    <hyperlink ref="A22" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C1EC1DA-CA57-42F4-A3AA-A0A0588F399B}"/>
-    <hyperlink ref="A11" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9785A814-9B30-4822-BC9E-D804419A01D1}"/>
+    <hyperlink ref="A20" r:id="rId1" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
+    <hyperlink ref="A19" r:id="rId2" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
+    <hyperlink ref="A23" r:id="rId3" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
+    <hyperlink ref="A16" r:id="rId4" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
+    <hyperlink ref="A9" r:id="rId5" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
+    <hyperlink ref="A2" r:id="rId6" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
+    <hyperlink ref="A18" r:id="rId7" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
+    <hyperlink ref="A26" r:id="rId8" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
+    <hyperlink ref="A6" r:id="rId9" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
+    <hyperlink ref="A17" r:id="rId10" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
+    <hyperlink ref="A24" r:id="rId11" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
+    <hyperlink ref="A3" r:id="rId12" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
+    <hyperlink ref="A4" r:id="rId13" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
+    <hyperlink ref="A29" r:id="rId14" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
+    <hyperlink ref="A5" r:id="rId15" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7668830C-59B8-4F92-879B-70324BB4D193}"/>
+    <hyperlink ref="A10" r:id="rId16" xr:uid="{4BA6EDCC-0531-4670-8770-157ADAE79A8E}"/>
+    <hyperlink ref="A7" r:id="rId17" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9D43AAAD-369E-43AE-836A-CE6A07DD65E2}"/>
+    <hyperlink ref="A14" r:id="rId18" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{54C5D1D3-C6E7-42ED-8E11-7CCA9C54BE78}"/>
+    <hyperlink ref="A28" r:id="rId19" xr:uid="{EBBB6BDC-96BE-4B7D-BE1C-1C8857858E2A}"/>
+    <hyperlink ref="A8" r:id="rId20" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{208417A7-5641-41CD-8C4F-D1A4EA68649D}"/>
+    <hyperlink ref="A13" r:id="rId21" xr:uid="{A0E64583-F066-467D-8CFA-63569F8AB875}"/>
+    <hyperlink ref="A27" r:id="rId22" xr:uid="{8FAE38C7-9C93-4CA9-9FF2-70DF5F01DDC1}"/>
+    <hyperlink ref="A22" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C1EC1DA-CA57-42F4-A3AA-A0A0588F399B}"/>
+    <hyperlink ref="A11" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9785A814-9B30-4822-BC9E-D804419A01D1}"/>
+    <hyperlink ref="A15" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg/1280px-L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D0B9E7DF-EC37-416B-B081-BD621C033893}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-18e-niveau1.xlsx
+++ b/quizzes/peinture-18e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EE9E43-E8F5-4228-AA03-AC11414BDE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CE61BE0-A972-4662-AD2D-9AF1C2964617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D010EE7-3957-4632-B43B-1193B29575F7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="135">
   <si>
     <t>image</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Le Pèlerinage à l'île de Cythère</t>
   </si>
   <si>
-    <t>Metropolitan Museum of Art, New York</t>
-  </si>
-  <si>
     <t>François Boucher</t>
   </si>
   <si>
@@ -80,27 +77,24 @@
     <t>Diane sortant du bain</t>
   </si>
   <si>
-    <t>1751</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/4/43/Joean_Honor%C3%A9_Fragonard_-_The_Swing.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+    <t>National Gallery of Art, Washington</t>
   </si>
   <si>
     <t>Jean-Honoré Fragonard</t>
   </si>
   <si>
-    <t>1767</t>
-  </si>
-  <si>
     <t>Wallace Collection, Londres</t>
   </si>
   <si>
-    <t>Les Hasards heureux de l'escarpolette</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/dc/Jean-Honor%C3%A9_Fragonard_009.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>1777</t>
   </si>
   <si>
+    <t>Le Verrou</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/94/La_Raie_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3197.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -122,18 +116,15 @@
     <t>Le Serment des Horaces</t>
   </si>
   <si>
-    <t>1787</t>
-  </si>
-  <si>
     <t>Château de Versailles</t>
   </si>
   <si>
-    <t>Marie-Antoinette et ses enfants</t>
-  </si>
-  <si>
     <t>National Gallery, Londres</t>
   </si>
   <si>
+    <t>1783</t>
+  </si>
+  <si>
     <t>Jean-Baptiste Greuze</t>
   </si>
   <si>
@@ -143,61 +134,46 @@
     <t>L'Accordée de village</t>
   </si>
   <si>
-    <t>1749</t>
-  </si>
-  <si>
-    <t>Jean-Marc Nattier</t>
-  </si>
-  <si>
-    <t>1748</t>
-  </si>
-  <si>
-    <t>Madame de Pompadour en Diane</t>
-  </si>
-  <si>
-    <t>1746</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/6a/Jean-Marc_Nattier%2C_Madame_de_Pompadour_en_Diane_%281746%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+    <t>1778</t>
   </si>
   <si>
     <t>Maurice Quentin de La Tour</t>
   </si>
   <si>
-    <t>Portrait de Voltaire</t>
-  </si>
-  <si>
-    <t>Musée Antoine-Lécuyer, Saint-Quentin</t>
-  </si>
-  <si>
-    <t>1735</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a1/Maurice_Quentin_de_La_Tour%2C_portrait_de_Voltaire_%281735%29_avec_agrandissement.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+    <t>Portrait de Madame de Pompadour</t>
+  </si>
+  <si>
+    <t>1748-1755</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/88/Maurice_Quentin_de_La_Tour_-_Marquise_de_Pompadour_-_WGA12359.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/4e/Deuxieme_vue_du_port_de_Bordeaux_prise_du_ch%C3%A2teau_Trompette.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>Claude Joseph Vernet</t>
   </si>
   <si>
-    <t>1773</t>
-  </si>
-  <si>
-    <t>La Tempête</t>
+    <t>1759</t>
+  </si>
+  <si>
+    <t>Musée national de la Marine, Paris</t>
+  </si>
+  <si>
+    <t>Vue du port de Bordeaux</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/1f/William_Hogarth_038.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>William Hogarth</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/5a/William_Hogarth_006.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>1745</t>
-  </si>
-  <si>
-    <t>Tate Britain, Londres</t>
-  </si>
-  <si>
-    <t>Le Peintre et son carlin (autoportrait au chien Trump)</t>
+    <t>1743</t>
+  </si>
+  <si>
+    <t>Le Mariage à la mode (I - Le Contrat de mariage)</t>
   </si>
   <si>
     <t>Joshua Reynolds</t>
@@ -215,39 +191,66 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Jean-Baptiste_Greuze_-_The_Village_Agreement.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/5/52/Thomas_Gainsborough_-_Mr_and_Mrs_Andrews.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Thomas Gainsborough</t>
   </si>
   <si>
-    <t>1750</t>
-  </si>
-  <si>
-    <t>Mr and Mrs Andrews</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/7e/Thomas_Gainsborough_-_The_Blue_Boy_%28The_Huntington_Library%2C_San_Marino_L._A.%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>1770</t>
   </si>
   <si>
+    <t>The Huntington, Californie</t>
+  </si>
+  <si>
+    <t>The Blue Boy</t>
+  </si>
+  <si>
     <t>1785</t>
   </si>
   <si>
-    <t>Johann Zoffany</t>
-  </si>
-  <si>
-    <t>1772-1778</t>
-  </si>
-  <si>
-    <t>Royal Collection, Windsor</t>
-  </si>
-  <si>
-    <t>The Tribuna of the Uffizi</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/48/Whistlejacket_by_George_Stubbs.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>George Stubbs</t>
+  </si>
+  <si>
+    <t>1762</t>
+  </si>
+  <si>
+    <t>Whistlejacket</t>
+  </si>
+  <si>
+    <t>1766</t>
+  </si>
+  <si>
+    <t>Scottish National Portrait Gallery, Édimbourg</t>
+  </si>
+  <si>
+    <t>Angelica Kauffman</t>
+  </si>
+  <si>
+    <t>Cornelia, mère des Gracques</t>
+  </si>
+  <si>
+    <t>Virginia Museum of Fine Arts, Richmond</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Kauffmann_Cornelia_mater_Gracchorum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>Museum of Fine Arts, Boston</t>
   </si>
   <si>
+    <t>John Singleton Copley</t>
+  </si>
+  <si>
+    <t>1768</t>
+  </si>
+  <si>
+    <t>Watson and the Shark</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/5e/Giambattista_Tiepolo_-_The_Banquet_of_Cleopatra_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -278,40 +281,13 @@
     <t>Francesco Guardi</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/3/3c/Francesco_Guardi_-_Santa_Maria_della_Salute_and_the_Dogana%2C_Venice_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Santa Maria della Salute et le Dogana</t>
-  </si>
-  <si>
-    <t>Musée des Beaux-Arts, Houston</t>
-  </si>
-  <si>
-    <t>Pietro Longhi</t>
-  </si>
-  <si>
-    <t>Ca'_Rezzonico, Venise</t>
-  </si>
-  <si>
-    <t>Le Rhinocéros</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/c/ca/Rosalba_Carriera_Self-portrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Rosalba Carriera</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>Galleria degli Uffizi, Florence</t>
-  </si>
-  <si>
-    <t>Autoportrait</t>
-  </si>
-  <si>
-    <t>Gemäldegalerie, Dresde</t>
+    <t>1775-1780</t>
+  </si>
+  <si>
+    <t>Le Doge sur le Bucentaure près de la Riva di Sant'Elena</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/96/Guardi_-_Le_D%C3%A9part_du_Bucentaure_vers_le_Lido_de_Venise%2C_le_jour_de_l%27Ascension%2C_vers_1770_-_1780%2C_INV_20009.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
     <t>Pompeo Batoni</t>
@@ -326,42 +302,12 @@
     <t>Portrait de Joseph II et Léopold de Toscane</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/02/Canaletto_-_Dresden_seen_from_the_Right_Bank_of_the_Elbe%2C_beneath_the_Augusts_Bridge_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Bernardo Bellotto</t>
-  </si>
-  <si>
-    <t>Vue de Dresde depuis la rive droite de l'Elbe</t>
-  </si>
-  <si>
     <t>Francisco de Goya</t>
   </si>
   <si>
     <t>El Quitasol (Le Parasol)</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Nature_morte_aux_figues%2C_par_Luis_Mel%C3%A9ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Luis Meléndez</t>
-  </si>
-  <si>
-    <t>Nature morte aux figues</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Anton_Raphael_Mengs_-_Parnassus_%28FondazioneTorlonia%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Anton Raphael Mengs</t>
-  </si>
-  <si>
-    <t>Villa Albani, Rome</t>
-  </si>
-  <si>
-    <t>Le Parnasse</t>
-  </si>
-  <si>
     <t>Henry Fuseli</t>
   </si>
   <si>
@@ -374,16 +320,16 @@
     <t>Le Cauchemar</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/e1/Louis_XIV_of_France_and_his_family_attributed_to_Nicolas_de_Largilli%C3%A8re.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Nicolas de Largillière</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>Louis XIV et sa famille</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f8/The_Death_of_General_Wolfe_B.West%2C1770.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Benjamin West</t>
+  </si>
+  <si>
+    <t>National Gallery of Canada, Ottawa</t>
+  </si>
+  <si>
+    <t>La Mort du général Wolfe</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Charles-Andr%C3%A9%2C_dit_Carle_Vanloo_-_Halte_de_chasse_%281737%29.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
@@ -404,19 +350,19 @@
     <t>Le chevreuil mort</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/23/Perronneau_Madame_de_Sorquainville.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Jean-Baptiste Perronneau</t>
-  </si>
-  <si>
-    <t>Portrait de Madame de Sorquainville</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8a/Ad%C3%A9la%C3%AFde_Labille-Guiard_-_Self-Portrait_with_Two_Pupils_-_The_Metropolitan_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Autoportrait avec deux élèves</t>
+    <t>Allan Ramsay</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d3/Allan_Ramsay_-_Jean-Jacques_Rousseau_%281712_-_1778%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Portrait de Jean-Jacques Rousseau</t>
+  </si>
+  <si>
+    <t>Joseph Wright of Derby</t>
+  </si>
+  <si>
+    <t>Une expérience sur un oiseau dans une pompe à air</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
@@ -425,7 +371,7 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/El_Quitasol_%28Goya%29.jpg/1280px-El_Quitasol_%28Goya%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
@@ -434,24 +380,15 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/33/Pompeo_Batoni_002.jpg/960px-Pompeo_Batoni_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/John_Henry_Fuseli_-_The_Nightmare.JPG/1280px-John_Henry_Fuseli_-_The_Nightmare.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg/960px-Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Watsonandtheshark-original.jpg/1280px-Watsonandtheshark-original.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Adélaïde LABILLE-GUIARD</t>
-  </si>
-  <si>
     <t>Carle van LOO</t>
   </si>
   <si>
@@ -459,6 +396,54 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg/1280px-L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/56/Hubert_Robert_-_Imaginary_View_of_the_Grande_Galerie_in_the_Louvre_in_Ruins_-_WGA19589.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Hubert Robert</t>
+  </si>
+  <si>
+    <t>Le Louvre en ruines</t>
+  </si>
+  <si>
+    <t>William Blake</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ac/Europe_a_Prophecy_copy_K_plate_01.jpg/960px-Europe_a_Prophecy_copy_K_plate_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Fitzwilliam Museum, l’Université de Cambridge.</t>
+  </si>
+  <si>
+    <t>L’Ancien des Jours ou Le Grand Architecte</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Girodet_-_Sommeil_Endymion.jpg/1280px-Girodet_-_Sommeil_Endymion.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Le Sommeil d’Endymion</t>
+  </si>
+  <si>
+    <t>Anne-Louis Girodet</t>
+  </si>
+  <si>
+    <t>François-Xavier Fabre</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/dd/VAlfieriFabre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Portrait du comte Vittorio Alfieri</t>
+  </si>
+  <si>
+    <t>Galérie des Offices, Florence</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg/960px-Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Marie-Antoinette avec une rose</t>
   </si>
 </sst>
 </file>
@@ -507,17 +492,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -528,9 +528,7 @@
       <top style="medium">
         <color rgb="FFA7402C"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFA7402C"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -539,9 +537,7 @@
       <top style="medium">
         <color rgb="FFA7402C"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFA7402C"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -552,9 +548,7 @@
       <top style="medium">
         <color rgb="FFA7402C"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFA7402C"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -562,24 +556,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -918,14 +916,14 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="51.28515625" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" customWidth="1"/>
     <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="52.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.75" thickBot="1">
+    <row r="1" spans="1:5" ht="30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -944,544 +942,542 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="A5" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="C5" s="5" t="s">
         <v>77</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>29</v>
+      <c r="D8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1783</v>
+      <c r="C9" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>99</v>
+      <c r="A10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>110</v>
+      <c r="E13" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="8" t="s">
+      <c r="A14" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="6">
+        <v>28</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="8">
         <v>1721</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="D18" s="5" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>39</v>
+      <c r="A21" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>67</v>
+      <c r="A22" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="4" t="s">
-        <v>100</v>
+      <c r="A24" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>94</v>
+      <c r="A28" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="9">
+        <v>1794</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>87</v>
+        <v>120</v>
+      </c>
+      <c r="C29" s="9">
+        <v>1796</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>58</v>
+      <c r="A30" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>60</v>
+        <v>128</v>
+      </c>
+      <c r="C30" s="9">
+        <v>1791</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>61</v>
+        <v>7</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>49</v>
+      <c r="A31" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>52</v>
+        <v>129</v>
+      </c>
+      <c r="C31" s="9">
+        <v>1794</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
-    <sortCondition ref="B2:B31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E27">
+    <sortCondition ref="B2:B27"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A20" r:id="rId1" xr:uid="{1C8DD03B-57E2-4D5D-87A2-5BBA570E562A}"/>
+    <hyperlink ref="A20" r:id="rId1" xr:uid="{35E3E0C5-7760-4EB4-A63D-8DC2B45AB000}"/>
     <hyperlink ref="A19" r:id="rId2" xr:uid="{9EB7565F-906C-4CAC-B7CA-7B2C2F95DC49}"/>
     <hyperlink ref="A23" r:id="rId3" xr:uid="{00B21B6F-99D8-4876-BED4-642AF6F093D2}"/>
-    <hyperlink ref="A16" r:id="rId4" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
-    <hyperlink ref="A9" r:id="rId5" xr:uid="{C2FC4FCB-36AA-44D2-A09E-52D3A186110D}"/>
-    <hyperlink ref="A2" r:id="rId6" xr:uid="{30E3C83A-CD6D-4CFC-A8DD-1FFFDA3C7B75}"/>
-    <hyperlink ref="A18" r:id="rId7" xr:uid="{E78676A6-0F13-46A5-A761-078D37818DE3}"/>
-    <hyperlink ref="A26" r:id="rId8" xr:uid="{E0E07521-79B5-4BA2-85D1-76F123D66818}"/>
-    <hyperlink ref="A6" r:id="rId9" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
-    <hyperlink ref="A17" r:id="rId10" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
-    <hyperlink ref="A24" r:id="rId11" xr:uid="{083AB9CA-F811-4290-8A7A-DD5442B9CAA0}"/>
-    <hyperlink ref="A3" r:id="rId12" xr:uid="{052C3565-C9B1-44B3-8B5D-F38676335856}"/>
-    <hyperlink ref="A4" r:id="rId13" xr:uid="{61B462A0-2A6A-43E2-ABD2-AC2F299E1A2F}"/>
-    <hyperlink ref="A29" r:id="rId14" xr:uid="{D02300E6-B445-47AF-97E4-7050501BFD07}"/>
-    <hyperlink ref="A5" r:id="rId15" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7668830C-59B8-4F92-879B-70324BB4D193}"/>
-    <hyperlink ref="A10" r:id="rId16" xr:uid="{4BA6EDCC-0531-4670-8770-157ADAE79A8E}"/>
-    <hyperlink ref="A7" r:id="rId17" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9D43AAAD-369E-43AE-836A-CE6A07DD65E2}"/>
-    <hyperlink ref="A14" r:id="rId18" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{54C5D1D3-C6E7-42ED-8E11-7CCA9C54BE78}"/>
-    <hyperlink ref="A28" r:id="rId19" xr:uid="{EBBB6BDC-96BE-4B7D-BE1C-1C8857858E2A}"/>
-    <hyperlink ref="A8" r:id="rId20" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg/960px-Marie_Antoinette_and_her_Children_by_%C3%89lisabeth_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{208417A7-5641-41CD-8C4F-D1A4EA68649D}"/>
-    <hyperlink ref="A13" r:id="rId21" xr:uid="{A0E64583-F066-467D-8CFA-63569F8AB875}"/>
-    <hyperlink ref="A27" r:id="rId22" xr:uid="{8FAE38C7-9C93-4CA9-9FF2-70DF5F01DDC1}"/>
-    <hyperlink ref="A22" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C1EC1DA-CA57-42F4-A3AA-A0A0588F399B}"/>
-    <hyperlink ref="A11" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9785A814-9B30-4822-BC9E-D804419A01D1}"/>
-    <hyperlink ref="A15" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg/1280px-L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D0B9E7DF-EC37-416B-B081-BD621C033893}"/>
+    <hyperlink ref="A17" r:id="rId4" xr:uid="{82552FB1-DCC4-41F5-8E8A-B3F6B05761BA}"/>
+    <hyperlink ref="A9" r:id="rId5" xr:uid="{A706DABA-E5F6-4965-92B2-0B4D8EECE9A9}"/>
+    <hyperlink ref="A2" r:id="rId6" xr:uid="{6052EA8F-A06C-4030-B911-93D5F34BB1AB}"/>
+    <hyperlink ref="A6" r:id="rId7" xr:uid="{FF077238-8E52-4F74-960B-358EB2A3BE52}"/>
+    <hyperlink ref="A18" r:id="rId8" xr:uid="{A3EF0CD1-997F-4FAC-B51D-7AD79A3CFE12}"/>
+    <hyperlink ref="A4" r:id="rId9" xr:uid="{A5D50A2F-BA88-4C06-8A5A-BC9406DFEE05}"/>
+    <hyperlink ref="A5" r:id="rId10" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{19411F62-23AF-4456-930D-FDDB2525D07E}"/>
+    <hyperlink ref="A10" r:id="rId11" xr:uid="{7239A756-B622-481B-B0CC-88BF1CDE0251}"/>
+    <hyperlink ref="A22" r:id="rId12" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C2E76D46-D38C-4C90-A0B4-6EDF62F894DD}"/>
+    <hyperlink ref="A15" r:id="rId13" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{352E471E-E731-4E5B-80BA-4999FF5F6B1A}"/>
+    <hyperlink ref="A25" r:id="rId14" xr:uid="{93456831-65A0-45D1-A1FF-595F7269BBE8}"/>
+    <hyperlink ref="A14" r:id="rId15" xr:uid="{CB0D0EC8-8997-41A5-91A6-A24DDA0FAC2A}"/>
+    <hyperlink ref="A21" r:id="rId16" xr:uid="{75A7E45B-C227-4CF5-B1E9-D5BDD9B6637C}"/>
+    <hyperlink ref="A16" r:id="rId17" display="https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg/1280px-L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F35051B9-00EE-460E-AC95-3A1849B7EDBE}"/>
+    <hyperlink ref="A29" r:id="rId18" xr:uid="{083149D2-D5A6-4EAD-9018-B0BB71385BD0}"/>
+    <hyperlink ref="A28" r:id="rId19" xr:uid="{5AF8E339-A65A-4370-83D5-F2CD280AB399}"/>
+    <hyperlink ref="A30" r:id="rId20" xr:uid="{1AD81FEF-E10B-4729-BFE0-D4E3F6E83CDE}"/>
+    <hyperlink ref="A31" r:id="rId21" xr:uid="{1CAAF61C-76A3-4554-9272-00E6BE85D621}"/>
+    <hyperlink ref="A11" r:id="rId22" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F832AFB4-5DD1-4747-88C1-8C98B2953930}"/>
+    <hyperlink ref="A8" r:id="rId23" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg/960px-Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F9575F1-8B45-47F6-BE9C-2AA500C217D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-18e-niveau1.xlsx
+++ b/quizzes/peinture-18e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CE61BE0-A972-4662-AD2D-9AF1C2964617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E4CFBB-9FD3-4927-A4F0-7FB8178DF1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D010EE7-3957-4632-B43B-1193B29575F7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="135">
   <si>
     <t>image</t>
   </si>
@@ -428,22 +428,22 @@
     <t>Anne-Louis Girodet</t>
   </si>
   <si>
-    <t>François-Xavier Fabre</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/dd/VAlfieriFabre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>Portrait du comte Vittorio Alfieri</t>
-  </si>
-  <si>
-    <t>Galérie des Offices, Florence</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg/960px-Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>Marie-Antoinette avec une rose</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/61/Hyacinthe_Rigaud_-_Louis_XIV%2C_roi_de_France_%281638-1715%29_-_Google_Art_Project.jpg/960px-Hyacinthe_Rigaud_-_Louis_XIV%2C_roi_de_France_%281638-1715%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Hyacinthe Rigaud</t>
+  </si>
+  <si>
+    <t>1701-1702</t>
+  </si>
+  <si>
+    <t>Louis XIV, roi de France </t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>117</v>
@@ -1056,7 +1056,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1435,19 +1435,19 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C31" s="9">
-        <v>1794</v>
-      </c>
-      <c r="D31" s="10" t="s">
         <v>132</v>
       </c>
+      <c r="C31" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="E31" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1475,9 +1475,9 @@
     <hyperlink ref="A29" r:id="rId18" xr:uid="{083149D2-D5A6-4EAD-9018-B0BB71385BD0}"/>
     <hyperlink ref="A28" r:id="rId19" xr:uid="{5AF8E339-A65A-4370-83D5-F2CD280AB399}"/>
     <hyperlink ref="A30" r:id="rId20" xr:uid="{1AD81FEF-E10B-4729-BFE0-D4E3F6E83CDE}"/>
-    <hyperlink ref="A31" r:id="rId21" xr:uid="{1CAAF61C-76A3-4554-9272-00E6BE85D621}"/>
-    <hyperlink ref="A11" r:id="rId22" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F832AFB4-5DD1-4747-88C1-8C98B2953930}"/>
-    <hyperlink ref="A8" r:id="rId23" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg/960px-Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F9575F1-8B45-47F6-BE9C-2AA500C217D3}"/>
+    <hyperlink ref="A11" r:id="rId21" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F832AFB4-5DD1-4747-88C1-8C98B2953930}"/>
+    <hyperlink ref="A8" r:id="rId22" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg/960px-Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F9575F1-8B45-47F6-BE9C-2AA500C217D3}"/>
+    <hyperlink ref="A31" r:id="rId23" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/61/Hyacinthe_Rigaud_-_Louis_XIV%2C_roi_de_France_%281638-1715%29_-_Google_Art_Project.jpg/960px-Hyacinthe_Rigaud_-_Louis_XIV%2C_roi_de_France_%281638-1715%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{540D88C4-6CB1-4689-BB79-EEA60E1B5C26}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-18e-niveau1.xlsx
+++ b/quizzes/peinture-18e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{245FE5DF-50EA-41F2-91C5-2AA0F0C191EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F1FEED6-3599-4D5F-A734-4274A2DDE1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="208">
   <si>
     <t>image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d3/Allan_Ramsay_-_Jean-Jacques_Rousseau_%281712_-_1778%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>75,9 × 62,9 cm</t>
   </si>
   <si>
+    <t>anglaise (Royaume-Uni)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Kauffmann_Cornelia_mater_Gracchorum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -91,6 +97,9 @@
     <t>101,6 × 127 cm</t>
   </si>
   <si>
+    <t>suisse</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f8/The_Death_of_General_Wolfe_B.West%2C1770.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -112,6 +121,9 @@
     <t>152,6 × 214,5 cm</t>
   </si>
   <si>
+    <t>américaine</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -133,6 +145,9 @@
     <t>125 × 204 cm</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Charles-Andr%C3%A9%2C_dit_Carle_Vanloo_-_Halte_de_chasse_%281737%29.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -154,6 +169,9 @@
     <t>216 × 276 cm</t>
   </si>
   <si>
+    <t>française</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/4/4e/Deuxieme_vue_du_port_de_Bordeaux_prise_du_ch%C3%A2teau_Trompette.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -233,6 +251,9 @@
   </si>
   <si>
     <t>104 × 152 cm</t>
+  </si>
+  <si>
+    <t>espagnole</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
@@ -1127,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -1140,7 +1161,7 @@
     <col min="8" max="8" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1">
+    <row r="1" spans="1:9" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1165,785 +1186,878 @@
       <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I14" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="7" t="s">
+      <c r="E15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I15" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>116</v>
+      </c>
+      <c r="I16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>122</v>
+      </c>
+      <c r="I17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C18" s="5">
         <v>1721</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>128</v>
+      </c>
+      <c r="I18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>134</v>
+      </c>
+      <c r="I19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>139</v>
+      </c>
+      <c r="I20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>146</v>
+      </c>
+      <c r="I21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>152</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>158</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>165</v>
+      </c>
+      <c r="I24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>172</v>
+      </c>
+      <c r="I25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>178</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>184</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C28" s="6">
         <v>1794</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>191</v>
+      </c>
+      <c r="I28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C29" s="6">
         <v>1796</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>196</v>
+      </c>
+      <c r="I29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C30" s="6">
         <v>1791</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>201</v>
+      </c>
+      <c r="I30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>200</v>
+        <v>207</v>
+      </c>
+      <c r="I31" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
